--- a/themes/paymentSchedule.xlsx
+++ b/themes/paymentSchedule.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -508,26 +508,6 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>55</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    isNotAuthorized: Для уточнения информации по графику платежей, напишите в чат приложения «Уралсиб Онлайн» или его [веб-версии](https://online.uralsib.ru/)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    isNotAuthorized: Для уточнения информации по графику платежей, напишите в чат приложения «Уралсиб Онлайн» или его [веб-версии](https://online.uralsib.ru/).</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
